--- a/www/download/IND.surplus_value.empe_ms.r.pc.rpA1.xlsx
+++ b/www/download/IND.surplus_value.empe_ms.r.pc.rpA1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>0.57996067501008</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>0.551135074787575</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>0.616983609426951</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>62.74</t>
+          <t>0.627416078515427</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>0.559313176866501</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>64.52</t>
+          <t>0.645180353700184</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>0.70020856067402</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>64.16</t>
+          <t>0.641593134576563</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>55.91</t>
+          <t>0.559102138013275</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>0.365029366551974</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>0.307396186683679</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>34.13</t>
+          <t>0.341280944726854</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>31.63</t>
+          <t>0.316273470690775</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>45.46</t>
+          <t>0.454560071451829</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>51.67</t>
+          <t>0.516706115514138</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>0.0566463462890672</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>0.102480858053682</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>29.69</t>
+          <t>0.296930641472973</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>27.72</t>
+          <t>0.277171043758921</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>0.27538108602531</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>0.338964455889116</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>32.57</t>
+          <t>0.325678713381709</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>0.324226961093697</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>0.264918308728176</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>0.202848623750213</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>0.180338295606166</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>16.22</t>
+          <t>0.162184282621724</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>0.159912958777265</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>0.214336110663612</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>31.08</t>
+          <t>0.310751370191331</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-16.6</t>
+          <t>-0.165965180532819</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-18.22</t>
+          <t>-0.182194311648616</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-14.17</t>
+          <t>-0.141695436517025</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-13.55</t>
+          <t>-0.135519273177154</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-20.39</t>
+          <t>-0.203858984721453</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-22.47</t>
+          <t>-0.224707877299321</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-26.66</t>
+          <t>-0.266613879587399</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-32.26</t>
+          <t>-0.322570358084833</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-42.6</t>
+          <t>-0.425979554601153</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-46.68</t>
+          <t>-0.466814795980524</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-45.48</t>
+          <t>-0.454827118757781</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-44.35</t>
+          <t>-0.443491328545501</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-41.91</t>
+          <t>-0.419116195453772</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-34.63</t>
+          <t>-0.346331219711657</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-37.88</t>
+          <t>-0.37882608506907</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>232.89</t>
+          <t>2.32888396852322</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>281.54</t>
+          <t>2.81538874992468</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>336.9</t>
+          <t>3.36899479887723</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>227.74</t>
+          <t>2.27737771277726</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>257.7</t>
+          <t>2.57701369348159</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>267.76</t>
+          <t>2.67764438924302</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>253.65</t>
+          <t>2.53650827420922</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>272.62</t>
+          <t>2.7261736517649</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>410.1</t>
+          <t>4.10101454931493</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>283.18</t>
+          <t>2.83176496233717</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>297.91</t>
+          <t>2.97909759652234</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>313.23</t>
+          <t>3.13231597461328</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>311.47</t>
+          <t>3.11467965199334</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>283.45</t>
+          <t>2.83453914242869</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>248.14</t>
+          <t>2.48137758802875</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>117.84</t>
+          <t>1.17838701490638</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>130.24</t>
+          <t>1.30235103532627</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>1.52497214873805</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>159.77</t>
+          <t>1.59771715135408</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>194.86</t>
+          <t>1.94861044759408</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>219.05</t>
+          <t>2.19054493788852</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>244.58</t>
+          <t>2.44584339907324</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>269.17</t>
+          <t>2.69172786922716</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>287.88</t>
+          <t>2.87875465095641</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>290.37</t>
+          <t>2.90367552514774</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>281.26</t>
+          <t>2.81264789856951</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>291.68</t>
+          <t>2.91676731092148</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>303.18</t>
+          <t>3.03180410444168</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>300.29</t>
+          <t>3.00286238661186</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>310.69</t>
+          <t>3.10687411518418</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>91.83</t>
+          <t>0.91830762345199</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>103.17</t>
+          <t>1.03171215866331</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>118.51</t>
+          <t>1.18513588422856</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>105.67</t>
+          <t>1.05666562346892</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>0.976959347341804</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>82.43</t>
+          <t>0.824284309658496</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>73.08</t>
+          <t>0.730754112492</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>0.742999849264316</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>63.24</t>
+          <t>0.632351017550464</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>57.96</t>
+          <t>0.579614223033122</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>0.466447483055532</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>0.42340301020786</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>0.490629142837106</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>0.517985556151322</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>0.640991779498896</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-39.43</t>
+          <t>-0.394322578536153</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-35.51</t>
+          <t>-0.355079044043213</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-35.31</t>
+          <t>-0.353142319921493</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-34.22</t>
+          <t>-0.342238550154449</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-32.95</t>
+          <t>-0.329509918646168</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-29.77</t>
+          <t>-0.297747014108626</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-22.31</t>
+          <t>-0.223075009063566</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-17.52</t>
+          <t>-0.175227812745977</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-10.46</t>
+          <t>-0.104617315332857</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.0106962187681036</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>0.0561920641520068</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>0.0932376939359914</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>0.252258071227522</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>29.18</t>
+          <t>0.291759762402396</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>0.341708324223671</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>112.89</t>
+          <t>1.1288540901278</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>107.48</t>
+          <t>1.07480924710283</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>137.07</t>
+          <t>1.37065612540148</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>127.4</t>
+          <t>1.2740294572608</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>110.77</t>
+          <t>1.10765556437285</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>117.72</t>
+          <t>1.17722479000063</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>96.63</t>
+          <t>0.966324934136144</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>93.97</t>
+          <t>0.939696706968776</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>77.27</t>
+          <t>0.772720949899547</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>81.12</t>
+          <t>0.811230312236562</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>83.89</t>
+          <t>0.838919548290482</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>92.58</t>
+          <t>0.925823388493278</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>116.66</t>
+          <t>1.16663241477637</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>89.85</t>
+          <t>0.898450973071728</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>132.37</t>
+          <t>1.32374471372794</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>391.6</t>
+          <t>3.91599933948799</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>244.92</t>
+          <t>2.44921525965676</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>271.43</t>
+          <t>2.71431430550455</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>265.15</t>
+          <t>2.6514581567248</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>269.42</t>
+          <t>2.69421683153146</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>286.15</t>
+          <t>2.86148990851408</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>253.22</t>
+          <t>2.53222972457906</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>240.91</t>
+          <t>2.40909541731342</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>210.37</t>
+          <t>2.10371166124128</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>192.62</t>
+          <t>1.9261629396543</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>184.54</t>
+          <t>1.845435532515</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>196.81</t>
+          <t>1.96814661063238</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>192.94</t>
+          <t>1.92940914530678</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>199.16</t>
+          <t>1.99157146603908</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>247.28</t>
+          <t>2.47280053524072</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-0.029634461645638</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>0.0675568913066726</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>0.214843970882387</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>0.193488665371118</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>0.149593009379386</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9.61</t>
+          <t>0.0961434437078856</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>0.124591085014303</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>13.86</t>
+          <t>0.138636375429196</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.00557425348193674</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.0186747201810963</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>0.0238766290294461</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>0.0343051580969624</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.0300357579372195</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>0.0972715436904461</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>14.44</t>
+          <t>0.144425951901075</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-13.93</t>
+          <t>-0.13929680898638</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>-0.116533691643196</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15.95</t>
+          <t>0.15953923023294</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>0.0696314843684702</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>0.0655801077976028</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>0.126220119616933</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>0.0865907431724147</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>0.0485154960182999</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-9.71</t>
+          <t>-0.0971051182963713</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-10.03</t>
+          <t>-0.10027508630943</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-10.13</t>
+          <t>-0.101340597717908</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-0.109384350004222</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>-10.3</t>
+          <t>-0.103048219042304</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-0.0326590405207846</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>0.0803841640398071</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>56.25</t>
+          <t>0.56249419701889</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>67.21</t>
+          <t>0.672070489623068</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>99.45</t>
+          <t>0.994471024649624</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>84.29</t>
+          <t>0.842943984045675</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>75.81</t>
+          <t>0.758109413250215</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>80.78</t>
+          <t>0.807759969742242</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>72.35</t>
+          <t>0.723489855043616</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>65.66</t>
+          <t>0.656634187762836</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>63.22</t>
+          <t>0.63222880687493</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>0.448850871433523</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>43.56</t>
+          <t>0.435555058871367</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>40.83</t>
+          <t>0.408314737807043</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>44.07</t>
+          <t>0.440650209505854</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>0.472159422873241</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>65.34</t>
+          <t>0.653411978414059</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>396.37</t>
+          <t>3.96371128343422</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>357.59</t>
+          <t>3.57590797709257</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>334.59</t>
+          <t>3.34588483126442</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>306.42</t>
+          <t>3.06415364847589</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>322.95</t>
+          <t>3.22951326249492</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>263.84</t>
+          <t>2.63839232901071</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>251.67</t>
+          <t>2.51671670497804</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>183.26</t>
+          <t>1.83256218254571</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>140.11</t>
+          <t>1.40107702228567</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>132.35</t>
+          <t>1.32350033385602</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>155.77</t>
+          <t>1.55769921423886</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>161.9</t>
+          <t>1.61896895613505</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>143.14</t>
+          <t>1.43143857192984</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>123.55</t>
+          <t>1.23554982029912</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>131.63</t>
+          <t>1.31633430403532</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>46.19</t>
+          <t>0.461884793825778</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>0.433299130277399</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>71.25</t>
+          <t>0.712450530756305</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.41</t>
+          <t>0.604087965663453</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>61.06</t>
+          <t>0.610577032280576</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>78.31</t>
+          <t>0.783143569519414</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>72.03</t>
+          <t>0.720306134461092</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>0.70600157697204</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>52.29</t>
+          <t>0.522871973976405</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>0.48438689425183</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>0.464647522128491</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>42.48</t>
+          <t>0.424790033418099</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>0.467416880160428</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>52.29</t>
+          <t>0.522869996645882</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>62.59</t>
+          <t>0.625949029418833</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>35.08</t>
+          <t>0.350837802685728</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>36.57</t>
+          <t>0.365717413085551</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>0.567695146595415</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>0.434983700223752</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>0.348022951429044</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>0.356254905592332</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>0.294500009631465</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>0.227787812692934</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>0.162968001910673</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>0.0906408867517228</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>0.0852359400977243</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>0.10425573703944</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>0.131902475914659</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>18.71</t>
+          <t>0.187145061835057</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>0.296496423542899</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>66.35</t>
+          <t>0.663491850976659</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>67.69</t>
+          <t>0.676928648644158</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>80.82</t>
+          <t>0.808165255409651</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>67.66</t>
+          <t>0.676596833128256</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>59.24</t>
+          <t>0.592383478576976</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>54.95</t>
+          <t>0.549485878189533</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>0.477574539479187</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>0.441463540636213</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>0.351484441992569</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>27.74</t>
+          <t>0.277390392114011</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>28.86</t>
+          <t>0.288620232363705</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>0.284623079930785</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>32.41</t>
+          <t>0.324109862929761</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>51.98</t>
+          <t>0.519794150391378</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>62.91</t>
+          <t>0.629149482355937</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>192.4</t>
+          <t>1.92396452327168</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>173.26</t>
+          <t>1.73263889347557</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>177.71</t>
+          <t>1.77710046611987</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>179.74</t>
+          <t>1.79743925690358</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>157.76</t>
+          <t>1.57755764383574</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>141.31</t>
+          <t>1.41305757398455</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>159.04</t>
+          <t>1.59038164335538</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>130.61</t>
+          <t>1.30612676732449</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>137.37</t>
+          <t>1.37366789084383</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>129.51</t>
+          <t>1.29508932456718</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>135.1</t>
+          <t>1.35102629926912</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>131.9</t>
+          <t>1.31898672161215</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>117.86</t>
+          <t>1.17860116442441</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>121.76</t>
+          <t>1.2176220741379</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>116.88</t>
+          <t>1.16878316842498</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>193.02</t>
+          <t>1.93018219259369</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>206.77</t>
+          <t>2.06770892397632</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>230.71</t>
+          <t>2.30711583296596</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>238.77</t>
+          <t>2.38766452972435</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>241.82</t>
+          <t>2.41823403529578</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>233.55</t>
+          <t>2.3354520541703</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>251.96</t>
+          <t>2.51960656240966</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>230.2</t>
+          <t>2.30195170382542</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>221.31</t>
+          <t>2.21314215832119</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>268.67</t>
+          <t>2.68670869559318</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>279.52</t>
+          <t>2.79521376821304</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>301.77</t>
+          <t>3.01770700900297</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>291.28</t>
+          <t>2.91277752101387</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>327.47</t>
+          <t>3.27471150360158</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>365.53</t>
+          <t>3.65534894103809</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>0.696551718763108</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>0.882045101565677</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>104.71</t>
+          <t>1.04714415569733</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>133.15</t>
+          <t>1.33148699103309</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>146.91</t>
+          <t>1.46905579750387</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>130.48</t>
+          <t>1.30480620520425</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>115.17</t>
+          <t>1.1517166977863</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>100.19</t>
+          <t>1.0019166615587</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>0.894868539652488</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>78.88</t>
+          <t>0.788760636804657</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>81.83</t>
+          <t>0.818288402108243</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>90.62</t>
+          <t>0.906203824191582</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>83.42</t>
+          <t>0.834157007503591</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>88.36</t>
+          <t>0.883555194072249</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>88.13</t>
+          <t>0.881277904581257</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.0174522403900195</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>0.0882770662862098</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>0.0494355364166481</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>0.0671950525528684</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>0.0995662027544608</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>0.158768872240658</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>19.38</t>
+          <t>0.193837387033411</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>0.278643251256476</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>0.268926776181149</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>26.01</t>
+          <t>0.260149266410788</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>0.224813704329714</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>0.191756802005236</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>23.16</t>
+          <t>0.231601702258726</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>0.282738434869682</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>0.235354236410791</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>62.19</t>
+          <t>0.62188722699895</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>59.02</t>
+          <t>0.590210731488244</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>82.24</t>
+          <t>0.822370194092266</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>0.906339551250816</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>0.914910380133942</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>88.83</t>
+          <t>0.888306633709552</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>72.16</t>
+          <t>0.721633033462054</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>0.6315550029816</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>83.57</t>
+          <t>0.835717127531161</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>94.04</t>
+          <t>0.940389339152822</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>0.857123933560116</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>95.25</t>
+          <t>0.952498259742799</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>84.73</t>
+          <t>0.847310037635941</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>72.39</t>
+          <t>0.723900654581354</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>56.24</t>
+          <t>0.562399932080086</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>50.81</t>
+          <t>0.508092227676381</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>53.14</t>
+          <t>0.531372209679167</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>66.48</t>
+          <t>0.664756895102396</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>65.85</t>
+          <t>0.658537935688831</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>65.55</t>
+          <t>0.65547787844309</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>70.17</t>
+          <t>0.701663708454124</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>56.48</t>
+          <t>0.564845837971757</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>0.50201083484841</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>48.43</t>
+          <t>0.484312696167514</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>27.92</t>
+          <t>0.279244543734799</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>0.267519885419601</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>24.52</t>
+          <t>0.245193411076141</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>0.305560583909869</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>0.434468060949254</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>58.83</t>
+          <t>0.588267154827874</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>39.76</t>
+          <t>0.397619015669476</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>0.595030293423413</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>77.38</t>
+          <t>0.773795453127039</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>84.49</t>
+          <t>0.844883874992209</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>72.99</t>
+          <t>0.72989346292604</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>64.06</t>
+          <t>0.640644198253327</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>0.674002957268746</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.76</t>
+          <t>0.767567662417061</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>71.96</t>
+          <t>0.719602807590138</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>64.16</t>
+          <t>0.641567672037056</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>62.91</t>
+          <t>0.629095956582437</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>71.42</t>
+          <t>0.71421805993074</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>0.892933822607016</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>94.62</t>
+          <t>0.946245801818772</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>87.16</t>
+          <t>0.871643050825339</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>100.35</t>
+          <t>1.00353302658387</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>104.61</t>
+          <t>1.0461449614557</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>125.55</t>
+          <t>1.25545487112779</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>153.78</t>
+          <t>1.53780585085848</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>162.25</t>
+          <t>1.62250558413571</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>149.42</t>
+          <t>1.49419272844156</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>157.28</t>
+          <t>1.57275083740123</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>149.71</t>
+          <t>1.49710708588125</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>133.49</t>
+          <t>1.33487272770161</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>133.45</t>
+          <t>1.33445459658902</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>134.97</t>
+          <t>1.3497042369984</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>127.84</t>
+          <t>1.27838496065283</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>131.85</t>
+          <t>1.31850171378235</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>153.63</t>
+          <t>1.53632210875849</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>168.79</t>
+          <t>1.68786909587815</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>306.07</t>
+          <t>3.06066871961136</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>284.7</t>
+          <t>2.84696108696577</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>287.31</t>
+          <t>2.873127903971</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>233.83</t>
+          <t>2.33826977935549</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>217.66</t>
+          <t>2.17663232026135</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>218.3</t>
+          <t>2.18295349229573</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>217.31</t>
+          <t>2.17309036214517</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>210.31</t>
+          <t>2.10309422990073</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>176.42</t>
+          <t>1.76418191719714</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>228.06</t>
+          <t>2.28057202495675</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>223.35</t>
+          <t>2.23348920350237</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>214.1</t>
+          <t>2.14102600012164</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>225.86</t>
+          <t>2.25858818665815</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>213.6</t>
+          <t>2.13595156447548</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>230.46</t>
+          <t>2.30463006431622</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-0.0365042526266918</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>12.17</t>
+          <t>0.121721386512584</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>34.91</t>
+          <t>0.34905906161811</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>0.411473713207148</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>0.384910936783051</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>0.383108553094263</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>51.06</t>
+          <t>0.510619536753047</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>0.421570486287324</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>43.79</t>
+          <t>0.437880930449529</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.393875844449332</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>0.369477057622643</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>0.388028599615136</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>60.45</t>
+          <t>0.604496877939519</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>44.39</t>
+          <t>0.44392907491394</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>79.62</t>
+          <t>0.796243059368529</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>336.66</t>
+          <t>3.36658675915238</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>298.26</t>
+          <t>2.98264306697279</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>312.96</t>
+          <t>3.12957482838554</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>312.47</t>
+          <t>3.12466934294575</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>313.42</t>
+          <t>3.13418350545689</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>382.34</t>
+          <t>3.82341096799459</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>385.77</t>
+          <t>3.85766839572154</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>404.4</t>
+          <t>4.04395632163344</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>371.19</t>
+          <t>3.71191459618382</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>381.77</t>
+          <t>3.81770745906816</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>354.36</t>
+          <t>3.54355535029583</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>321.77</t>
+          <t>3.2176867054213</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>270.26</t>
+          <t>2.70259406353898</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>247.42</t>
+          <t>2.47422731341905</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>311.6</t>
+          <t>3.11596673048841</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>218.78</t>
+          <t>2.1878180271869</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>234.78</t>
+          <t>2.34779114842624</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>268.12</t>
+          <t>2.68119417797754</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>242.66</t>
+          <t>2.42656774022453</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>227.46</t>
+          <t>2.27462375313154</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>221.05</t>
+          <t>2.21052079844072</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>193.42</t>
+          <t>1.93420218281439</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>198.35</t>
+          <t>1.98352529964055</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>205.12</t>
+          <t>2.05118186687291</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>225.88</t>
+          <t>2.25881282056615</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>230.07</t>
+          <t>2.30070021400918</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>255.8</t>
+          <t>2.55801152872961</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>269.09</t>
+          <t>2.69088089786948</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>274.55</t>
+          <t>2.7455408706201</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>277.45</t>
+          <t>2.77445857761762</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>121.98</t>
+          <t>1.21975473249526</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>108.3</t>
+          <t>1.08296640573705</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>152.46</t>
+          <t>1.52462504310808</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>132.42</t>
+          <t>1.32423609124083</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>105.19</t>
+          <t>1.05185841461544</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>93.47</t>
+          <t>0.934670865780862</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>0.462015835106583</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>62.91</t>
+          <t>0.62907696583577</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>91.83</t>
+          <t>0.918284984816269</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>89.63</t>
+          <t>0.896315049804624</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>90.55</t>
+          <t>0.905487089933853</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>100.44</t>
+          <t>1.00444605465464</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>93.16</t>
+          <t>0.931632596277197</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>0.85303303632911</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>111.05</t>
+          <t>1.11046904441536</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-27.2</t>
+          <t>-0.271964361130664</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-23.69</t>
+          <t>-0.23690270484133</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>0.127240879081695</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-0.0708361489570413</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-9.83</t>
+          <t>-0.0982620648260669</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-0.0638073707995481</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-15.09</t>
+          <t>-0.150928874218678</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-23.19</t>
+          <t>-0.231935467097712</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-17.74</t>
+          <t>-0.17742669555775</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-19.22</t>
+          <t>-0.192190969508124</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-15.88</t>
+          <t>-0.158755336307736</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-15.94</t>
+          <t>-0.159374487034648</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-0.170030721534781</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-18.51</t>
+          <t>-0.185080231350783</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-15.2</t>
+          <t>-0.151986661798611</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>101.2</t>
+          <t>1.01198524153651</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>0.89921429759157</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>0.884074647490461</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>0.82696741218823</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>97.92</t>
+          <t>0.979197666806859</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>1.10995720795135</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>173.63</t>
+          <t>1.73631304328791</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>187.65</t>
+          <t>1.87648308934115</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>203.26</t>
+          <t>2.03261987450399</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>228.78</t>
+          <t>2.28782272151407</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>218.64</t>
+          <t>2.18644670233057</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>230.14</t>
+          <t>2.30142686809425</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>236.03</t>
+          <t>2.36030625556695</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>216.16</t>
+          <t>2.16158481214585</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>250.28</t>
+          <t>2.50281038646706</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>60.88</t>
+          <t>0.608818600576983</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>58.36</t>
+          <t>0.583606467016712</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>0.808951044221472</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>62.88</t>
+          <t>0.628837715198554</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>69.08</t>
+          <t>0.690776489112724</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>68.67</t>
+          <t>0.686679640012482</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>61.38</t>
+          <t>0.613830602618803</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>65.33</t>
+          <t>0.653324873883943</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>119.71</t>
+          <t>1.19706893683387</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>70.15</t>
+          <t>0.701525352765167</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>74.17</t>
+          <t>0.741733226266273</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>97.99</t>
+          <t>0.979899316153103</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>1.03496224285499</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>99.78</t>
+          <t>0.997811263111546</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>135.95</t>
+          <t>1.35952362896903</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>98.57</t>
+          <t>0.985711374321946</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>109.1</t>
+          <t>1.09096404511818</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>126.01</t>
+          <t>1.26006318731774</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>86.79</t>
+          <t>0.867880523503079</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>80.77</t>
+          <t>0.807677048499822</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>56.16</t>
+          <t>0.561572164280187</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>51.62</t>
+          <t>0.516233847351711</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>107.54</t>
+          <t>1.07544499040399</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>187.11</t>
+          <t>1.87109556750408</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>148.78</t>
+          <t>1.48776409665047</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>124.4</t>
+          <t>1.24398108113329</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>134.05</t>
+          <t>1.3405218086518</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>121.73</t>
+          <t>1.21730082781424</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>110.81</t>
+          <t>1.10810521456596</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>136.05</t>
+          <t>1.36046104747505</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>121.38</t>
+          <t>1.21378198785191</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>1.10000269047903</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>131.26</t>
+          <t>1.3125695691231</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>145.11</t>
+          <t>1.45114502588889</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>161.66</t>
+          <t>1.61660736225545</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>135.11</t>
+          <t>1.35114087551413</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>144.39</t>
+          <t>1.44388647209565</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>140.25</t>
+          <t>1.40246764944077</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>122.49</t>
+          <t>1.22487674146809</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>114.99</t>
+          <t>1.14985635033958</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>110.88</t>
+          <t>1.10876116950816</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>114.16</t>
+          <t>1.14162749647245</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>0.95010540817104</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>71.44</t>
+          <t>0.71435824521598</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>71.59</t>
+          <t>0.71593528455562</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>444.11</t>
+          <t>4.44106768134552</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>411.67</t>
+          <t>4.11668909650834</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>427.06</t>
+          <t>4.27061320473113</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>420.11</t>
+          <t>4.20106095895447</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>456.98</t>
+          <t>4.56979443772493</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>445.74</t>
+          <t>4.45743541874271</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>429.14</t>
+          <t>4.29140503864618</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>414.04</t>
+          <t>4.14041223302535</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>350.69</t>
+          <t>3.50685370035074</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>273.61</t>
+          <t>2.73605351796025</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>284.81</t>
+          <t>2.84807722447387</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>263.39</t>
+          <t>2.63390180045244</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>203.52</t>
+          <t>2.03518196214709</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>218.23</t>
+          <t>2.18226912537666</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>162.86</t>
+          <t>1.62864200676682</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>66.17</t>
+          <t>0.661684955939562</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>71.68</t>
+          <t>0.71682592494058</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>92.91</t>
+          <t>0.929132575002861</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>0.831027068892701</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>83.32</t>
+          <t>0.833202590914867</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>0.909034556999859</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>80.78</t>
+          <t>0.80775003329676</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>81.59</t>
+          <t>0.81593795012901</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>66.77</t>
+          <t>0.667734239745993</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>77.34</t>
+          <t>0.773354648508563</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>85.97</t>
+          <t>0.859650926173568</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>86.21</t>
+          <t>0.862135227305282</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>92.33</t>
+          <t>0.923253717068489</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>41.68</t>
+          <t>0.416757671821848</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>0.461218323109462</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>0.346504706947899</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>0.312519657957105</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>0.512986393774153</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>40.63</t>
+          <t>0.406284480656395</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>41.02</t>
+          <t>0.410194781936543</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>31.14</t>
+          <t>0.311419735786957</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>0.304454850738159</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>0.258079740568052</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>0.16557118940932</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>0.131449275243201</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>0.102611461528128</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>0.112130376443693</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>0.0906192889190516</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>0.239434777910275</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>0.407360057696001</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>152.49</t>
+          <t>1.52486651730782</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>129.35</t>
+          <t>1.29351113312329</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>126.08</t>
+          <t>1.26083527686201</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>125.23</t>
+          <t>1.25226837657965</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>106.17</t>
+          <t>1.06174415620568</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>1.47996177015958</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>170.16</t>
+          <t>1.70157972526462</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>221.99</t>
+          <t>2.21985192847173</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>217.58</t>
+          <t>2.17575387837568</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>189.94</t>
+          <t>1.8993665199519</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>209.49</t>
+          <t>2.09485522593269</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>224.36</t>
+          <t>2.2435950986192</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>221.61</t>
+          <t>2.21608427571146</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>89.62</t>
+          <t>0.896243653997743</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>115.17</t>
+          <t>1.1516764386444</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>65.82</t>
+          <t>0.658182605722093</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>56.66</t>
+          <t>0.566577538723551</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>77.76</t>
+          <t>0.777635588411477</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>86.26</t>
+          <t>0.862644236946448</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>91.99</t>
+          <t>0.91986877697804</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>83.97</t>
+          <t>0.839671114942814</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>79.95</t>
+          <t>0.799478729052185</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>85.62</t>
+          <t>0.856179036262401</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>86.65</t>
+          <t>0.866477586793467</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>90.96</t>
+          <t>0.909588606978349</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>94.21</t>
+          <t>0.942148877245942</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>103.63</t>
+          <t>1.03631742050102</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>129.01</t>
+          <t>1.29009023840461</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>133.65</t>
+          <t>1.33648070439672</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>158.89</t>
+          <t>1.58894045300099</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>98.13</t>
+          <t>0.981252681083073</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>102.71</t>
+          <t>1.02713743848267</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>105.3</t>
+          <t>1.05302030640968</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>95.75</t>
+          <t>0.957494193123214</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>89.26</t>
+          <t>0.892648805777819</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>76.61</t>
+          <t>0.766124946523622</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>70.04</t>
+          <t>0.700399481893014</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>64.13</t>
+          <t>0.641255425431836</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>0.593041153658132</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>0.589715782207848</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>58.41</t>
+          <t>0.584127434294385</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>64.96</t>
+          <t>0.649603208018224</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>0.756984514499002</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>88.71</t>
+          <t>0.887103476889034</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>94.39</t>
+          <t>0.943916173478742</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>-17.24</t>
+          <t>-0.172392171358465</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-12.82</t>
+          <t>-0.128204309457241</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>-13.57</t>
+          <t>-0.135684616468941</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-13.88</t>
+          <t>-0.138817037528654</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-0.146242749344092</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-15.5</t>
+          <t>-0.154976056001764</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-14.13</t>
+          <t>-0.141272121898506</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-11.74</t>
+          <t>-0.117433721473009</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-0.0431120472827798</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>0.0136369141746975</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.0172460358048483</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>0.0319617212493239</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>12.73</t>
+          <t>0.127326166239921</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>0.167305262709559</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>21.57</t>
+          <t>0.215679721535705</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0.0943585570031105</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>14.48</t>
+          <t>0.144837828821637</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>0.160367281185834</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>0.158027273081425</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>0.157394169457122</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>0.151610677268899</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>17.03</t>
+          <t>0.170337370125202</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>0.192934852767914</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>0.227254142891687</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>0.265314958250543</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>0.276522798545011</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>29.97</t>
+          <t>0.299743224306414</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>0.390462474196212</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>0.427014160184548</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>46.19</t>
+          <t>0.461896104418783</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA1</t>
